--- a/Kiem Thu Chuc Nang/Kiểm thử giá trị biên.xlsx
+++ b/Kiem Thu Chuc Nang/Kiểm thử giá trị biên.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\test-and-qa\Kiem Thu Chuc Nang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3343FC-293A-4B9A-AEFE-C4972F7C9AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10CCAB7-A172-4174-90CE-9BD23E7FC19A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4EB93EE9-2C44-4CA1-B0A9-E74947662805}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="47">
   <si>
     <t>Giá trị biên của từng biến</t>
   </si>
@@ -171,6 +171,12 @@
   </si>
   <si>
     <t>INVALID</t>
+  </si>
+  <si>
+    <t>Trạng thái</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
@@ -234,12 +240,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -576,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CA37DD2-B20E-4B1B-896A-8FC40F59F2C3}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -584,9 +593,10 @@
     <col min="15" max="15" width="12.109375" customWidth="1"/>
     <col min="16" max="16" width="16.109375" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -611,8 +621,11 @@
       <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R1" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -649,8 +662,9 @@
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -693,8 +707,11 @@
       <c r="Q3" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R3" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -737,8 +754,11 @@
       <c r="Q4" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R4" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -781,8 +801,11 @@
       <c r="Q5" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R5" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -825,8 +848,11 @@
       <c r="Q6" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R6" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -869,8 +895,11 @@
       <c r="Q7" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R7" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J8" s="1" t="s">
         <v>21</v>
       </c>
@@ -895,8 +924,11 @@
       <c r="Q8" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R8" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J9" s="1" t="s">
         <v>22</v>
       </c>
@@ -921,8 +953,11 @@
       <c r="Q9" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R9" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J10" s="1" t="s">
         <v>23</v>
       </c>
@@ -947,8 +982,11 @@
       <c r="Q10" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R10" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J11" s="1" t="s">
         <v>24</v>
       </c>
@@ -973,8 +1011,11 @@
       <c r="Q11" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R11" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J12" s="1" t="s">
         <v>25</v>
       </c>
@@ -999,8 +1040,11 @@
       <c r="Q12" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R12" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1025,8 +1069,11 @@
       <c r="Q13" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J14" s="1" t="s">
         <v>27</v>
       </c>
@@ -1051,8 +1098,11 @@
       <c r="Q14" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R14" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J15" s="1" t="s">
         <v>28</v>
       </c>
@@ -1077,8 +1127,11 @@
       <c r="Q15" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R15" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J16" s="1" t="s">
         <v>29</v>
       </c>
@@ -1103,8 +1156,11 @@
       <c r="Q16" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="17" spans="10:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R16" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="10:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J17" s="1" t="s">
         <v>30</v>
       </c>
@@ -1129,8 +1185,11 @@
       <c r="Q17" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="18" spans="10:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R17" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="10:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J18" s="1" t="s">
         <v>31</v>
       </c>
@@ -1155,8 +1214,11 @@
       <c r="Q18" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" spans="10:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R18" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="10:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1181,8 +1243,11 @@
       <c r="Q19" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="10:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R19" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="10:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J20" s="1" t="s">
         <v>33</v>
       </c>
@@ -1207,8 +1272,11 @@
       <c r="Q20" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="21" spans="10:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R20" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="10:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J21" s="1" t="s">
         <v>34</v>
       </c>
@@ -1233,8 +1301,11 @@
       <c r="Q21" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="22" spans="10:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R21" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="10:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J22" s="1" t="s">
         <v>35</v>
       </c>
@@ -1259,8 +1330,11 @@
       <c r="Q22" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="10:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R22" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="10:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J23" s="1" t="s">
         <v>36</v>
       </c>
@@ -1285,8 +1359,11 @@
       <c r="Q23" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="24" spans="10:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="R23" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="10:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J24" s="1" t="s">
         <v>43</v>
       </c>
@@ -1311,9 +1388,13 @@
       <c r="Q24" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="R24" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="R1:R2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="J1:J2"/>
